--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>70.51479999999999</v>
+        <v>81.0545</v>
       </c>
       <c r="E2" t="n">
-        <v>49.7046</v>
+        <v>57.8291</v>
       </c>
       <c r="F2" t="n">
-        <v>20.8102</v>
+        <v>23.2254</v>
       </c>
       <c r="G2" t="n">
-        <v>68.5929</v>
+        <v>46.5209</v>
       </c>
       <c r="H2" t="n">
-        <v>13.676</v>
+        <v>20.3071</v>
       </c>
       <c r="I2" t="n">
-        <v>54.9174</v>
+        <v>26.2135</v>
       </c>
       <c r="J2" t="n">
-        <v>86.1634</v>
+        <v>59.507</v>
       </c>
       <c r="K2" t="n">
-        <v>27.9715</v>
+        <v>26.933</v>
       </c>
       <c r="L2" t="n">
-        <v>58.1919</v>
+        <v>32.5743</v>
       </c>
       <c r="M2" t="n">
-        <v>-17.5704</v>
+        <v>-12.9865</v>
       </c>
       <c r="N2" t="n">
-        <v>-14.2958</v>
+        <v>-6.6258</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.2751</v>
+        <v>-6.361</v>
       </c>
       <c r="P2" t="n">
-        <v>-10.0616</v>
+        <v>5.954899999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-51.5406</v>
+        <v>-44.1487</v>
       </c>
       <c r="R2" t="n">
-        <v>41.4792</v>
+        <v>50.1036</v>
       </c>
       <c r="S2" t="n">
-        <v>1.765500000000001</v>
+        <v>4.3997</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.5479</v>
+        <v>1.631</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3132</v>
+        <v>2.7686</v>
       </c>
       <c r="V2" t="n">
-        <v>10.2181</v>
+        <v>24.1791</v>
       </c>
       <c r="W2" t="n">
-        <v>20.6297</v>
+        <v>40.839</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.4115</v>
+        <v>-16.6602</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>65.9794</v>
+        <v>80.4126</v>
       </c>
       <c r="E3" t="n">
-        <v>47.1788</v>
+        <v>60.1072</v>
       </c>
       <c r="F3" t="n">
-        <v>18.8003</v>
+        <v>20.306</v>
       </c>
       <c r="G3" t="n">
-        <v>46.5209</v>
+        <v>68.5929</v>
       </c>
       <c r="H3" t="n">
-        <v>20.3071</v>
+        <v>13.676</v>
       </c>
       <c r="I3" t="n">
-        <v>26.2135</v>
+        <v>54.9174</v>
       </c>
       <c r="J3" t="n">
-        <v>59.507</v>
+        <v>86.1634</v>
       </c>
       <c r="K3" t="n">
-        <v>26.933</v>
+        <v>27.9715</v>
       </c>
       <c r="L3" t="n">
-        <v>32.5743</v>
+        <v>58.1919</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.9865</v>
+        <v>-17.5704</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.6258</v>
+        <v>-14.2958</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.361</v>
+        <v>-3.2751</v>
       </c>
       <c r="P3" t="n">
-        <v>5.954899999999999</v>
+        <v>-10.0616</v>
       </c>
       <c r="Q3" t="n">
-        <v>-44.1487</v>
+        <v>-51.5406</v>
       </c>
       <c r="R3" t="n">
-        <v>50.1036</v>
+        <v>41.4792</v>
       </c>
       <c r="S3" t="n">
-        <v>-10.6755</v>
+        <v>11.6634</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.0192</v>
+        <v>4.8544</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6565</v>
+        <v>6.809</v>
       </c>
       <c r="V3" t="n">
-        <v>24.1791</v>
+        <v>10.2181</v>
       </c>
       <c r="W3" t="n">
-        <v>40.839</v>
+        <v>20.6297</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.6602</v>
+        <v>-10.4115</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>48.7589</v>
+        <v>42.3199</v>
       </c>
       <c r="E4" t="n">
-        <v>25.0697</v>
+        <v>20.6029</v>
       </c>
       <c r="F4" t="n">
-        <v>23.6894</v>
+        <v>21.7171</v>
       </c>
       <c r="G4" t="n">
         <v>16.3727</v>
@@ -766,13 +766,13 @@
         <v>35.1135</v>
       </c>
       <c r="S4" t="n">
-        <v>23.8617</v>
+        <v>17.4224</v>
       </c>
       <c r="T4" t="n">
-        <v>14.4554</v>
+        <v>9.9886</v>
       </c>
       <c r="U4" t="n">
-        <v>9.4062</v>
+        <v>7.4338</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1531</v>
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>36.5999</v>
+        <v>25.6083</v>
       </c>
       <c r="E5" t="n">
-        <v>33.8592</v>
+        <v>20.3693</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7405</v>
+        <v>5.2387</v>
       </c>
       <c r="G5" t="n">
         <v>12.1075</v>
@@ -844,13 +844,13 @@
         <v>40.4525</v>
       </c>
       <c r="S5" t="n">
-        <v>23.9345</v>
+        <v>12.9434</v>
       </c>
       <c r="T5" t="n">
-        <v>21.9667</v>
+        <v>8.4772</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9677</v>
+        <v>4.4663</v>
       </c>
       <c r="V5" t="n">
         <v>-7.2452</v>
@@ -877,13 +877,13 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>20.9267</v>
+        <v>23.4752</v>
       </c>
       <c r="E6" t="n">
-        <v>21.1787</v>
+        <v>21.0664</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2520000000000003</v>
+        <v>2.4084</v>
       </c>
       <c r="G6" t="n">
         <v>9.068</v>
@@ -922,13 +922,13 @@
         <v>32.6496</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1481999999999998</v>
+        <v>2.4004</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7215999999999998</v>
+        <v>0.6092</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8695000000000002</v>
+        <v>1.7911</v>
       </c>
       <c r="V6" t="n">
         <v>3.5876</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2883</v>
+        <v>17.7846</v>
       </c>
       <c r="E7" t="n">
-        <v>21.1367</v>
+        <v>7.197300000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.8483</v>
+        <v>10.5871</v>
       </c>
       <c r="G7" t="n">
-        <v>6.674200000000001</v>
+        <v>41.0388</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0474</v>
+        <v>18.7494</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6269</v>
+        <v>22.2896</v>
       </c>
       <c r="J7" t="n">
-        <v>14.4525</v>
+        <v>60.362</v>
       </c>
       <c r="K7" t="n">
-        <v>6.0754</v>
+        <v>28.9429</v>
       </c>
       <c r="L7" t="n">
-        <v>8.376999999999999</v>
+        <v>31.4191</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.7785</v>
+        <v>-19.3233</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.0281</v>
+        <v>-10.1938</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7504</v>
+        <v>-9.1295</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8481</v>
+        <v>-27.3106</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11.0885</v>
+        <v>-70.4323</v>
       </c>
       <c r="R7" t="n">
-        <v>12.9367</v>
+        <v>43.1218</v>
       </c>
       <c r="S7" t="n">
-        <v>8.1289</v>
+        <v>-1.5795</v>
       </c>
       <c r="T7" t="n">
-        <v>8.212100000000001</v>
+        <v>-0.2167999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08319999999999994</v>
+        <v>-1.3625</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3625</v>
+        <v>5.6355</v>
       </c>
       <c r="W7" t="n">
-        <v>9.560400000000001</v>
+        <v>17.4841</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.9229</v>
+        <v>-11.8485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>12.7396</v>
+        <v>11.148</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6903</v>
+        <v>16.3794</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.950600000000001</v>
+        <v>-5.2312</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.894000000000001</v>
+        <v>6.674200000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-9.2195</v>
+        <v>1.0474</v>
       </c>
       <c r="I8" t="n">
-        <v>6.325899999999999</v>
+        <v>5.6269</v>
       </c>
       <c r="J8" t="n">
-        <v>18.0685</v>
+        <v>14.4525</v>
       </c>
       <c r="K8" t="n">
-        <v>4.301</v>
+        <v>6.0754</v>
       </c>
       <c r="L8" t="n">
-        <v>13.767</v>
+        <v>8.376999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-20.9621</v>
+        <v>-7.7785</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.5211</v>
+        <v>-5.0281</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.4415</v>
+        <v>-2.7504</v>
       </c>
       <c r="P8" t="n">
-        <v>6.9816</v>
+        <v>1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.4891</v>
+        <v>-11.0885</v>
       </c>
       <c r="R8" t="n">
-        <v>33.4707</v>
+        <v>12.9367</v>
       </c>
       <c r="S8" t="n">
-        <v>11.3343</v>
+        <v>3.9886</v>
       </c>
       <c r="T8" t="n">
-        <v>8.7912</v>
+        <v>3.4545</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5429</v>
+        <v>0.5338999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6825</v>
+        <v>-1.3625</v>
       </c>
       <c r="W8" t="n">
-        <v>14.3198</v>
+        <v>9.560400000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.0024</v>
+        <v>-10.9229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>9.643500000000001</v>
+        <v>10.183</v>
       </c>
       <c r="E9" t="n">
-        <v>7.3025</v>
+        <v>13.1139</v>
       </c>
       <c r="F9" t="n">
-        <v>2.341199999999999</v>
+        <v>-2.9309</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1183</v>
+        <v>-2.894000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>12.1629</v>
+        <v>-9.2195</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0446</v>
+        <v>6.325899999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>17.2162</v>
+        <v>18.0685</v>
       </c>
       <c r="K9" t="n">
-        <v>13.4273</v>
+        <v>4.301</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7887</v>
+        <v>13.767</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.0978</v>
+        <v>-20.9621</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2644</v>
+        <v>-13.5211</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.8331</v>
+        <v>-7.4415</v>
       </c>
       <c r="P9" t="n">
-        <v>-12.5258</v>
+        <v>6.9816</v>
       </c>
       <c r="Q9" t="n">
-        <v>-31.0064</v>
+        <v>-26.4891</v>
       </c>
       <c r="R9" t="n">
-        <v>18.4809</v>
+        <v>33.4707</v>
       </c>
       <c r="S9" t="n">
-        <v>7.6336</v>
+        <v>8.7776</v>
       </c>
       <c r="T9" t="n">
-        <v>8.060499999999999</v>
+        <v>7.2145</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4265000000000001</v>
+        <v>1.5629</v>
       </c>
       <c r="V9" t="n">
-        <v>3.4173</v>
+        <v>-2.6825</v>
       </c>
       <c r="W9" t="n">
-        <v>13.0324</v>
+        <v>14.3198</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.6152</v>
+        <v>-17.0024</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>3.704400000000001</v>
+        <v>4.585400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.244000000000001</v>
+        <v>2.208</v>
       </c>
       <c r="F10" t="n">
-        <v>6.9482</v>
+        <v>2.3777</v>
       </c>
       <c r="G10" t="n">
-        <v>41.0388</v>
+        <v>11.1183</v>
       </c>
       <c r="H10" t="n">
-        <v>18.7494</v>
+        <v>12.1629</v>
       </c>
       <c r="I10" t="n">
-        <v>22.2896</v>
+        <v>-1.0446</v>
       </c>
       <c r="J10" t="n">
-        <v>60.362</v>
+        <v>17.2162</v>
       </c>
       <c r="K10" t="n">
-        <v>28.9429</v>
+        <v>13.4273</v>
       </c>
       <c r="L10" t="n">
-        <v>31.4191</v>
+        <v>3.7887</v>
       </c>
       <c r="M10" t="n">
-        <v>-19.3233</v>
+        <v>-6.0978</v>
       </c>
       <c r="N10" t="n">
-        <v>-10.1938</v>
+        <v>-1.2644</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.1295</v>
+        <v>-4.8331</v>
       </c>
       <c r="P10" t="n">
-        <v>-27.3106</v>
+        <v>-12.5258</v>
       </c>
       <c r="Q10" t="n">
-        <v>-70.4323</v>
+        <v>-31.0064</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1218</v>
+        <v>18.4809</v>
       </c>
       <c r="S10" t="n">
-        <v>-15.6598</v>
+        <v>2.5758</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.6578</v>
+        <v>2.966</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.0016</v>
+        <v>-0.3902999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>5.6355</v>
+        <v>3.4173</v>
       </c>
       <c r="W10" t="n">
-        <v>17.4841</v>
+        <v>13.0324</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.8485</v>
+        <v>-9.6152</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2.0808</v>
+        <v>2.6161</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9996</v>
+        <v>1.2088</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0812</v>
+        <v>1.4073</v>
       </c>
       <c r="G11" t="n">
         <v>2.7086</v>
@@ -1312,13 +1312,13 @@
         <v>1.848</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3723</v>
+        <v>0.9075</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1123</v>
+        <v>0.3215</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2601</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7286999999999999</v>
+        <v>1.7845</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6386000000000001</v>
+        <v>0.1208</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3673</v>
+        <v>1.6638</v>
       </c>
       <c r="G12" t="n">
         <v>0.349</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4766</v>
+        <v>0.5791999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7906000000000001</v>
+        <v>-0.03120000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.314</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.2402</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8135</v>
+        <v>-0.436700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0718</v>
+        <v>5.1385</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2583</v>
+        <v>-5.575299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.505</v>
+        <v>5.9079</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8629</v>
+        <v>1.5368</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3579</v>
+        <v>4.371</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6183999999999999</v>
+        <v>17.8003</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6974</v>
+        <v>12.246</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0789</v>
+        <v>5.5543</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1134</v>
+        <v>-11.8928</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1656</v>
+        <v>-10.7094</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2789</v>
+        <v>-1.1834</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8214</v>
+        <v>3.0802</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>-19.3019</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2053</v>
+        <v>22.3825</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5129</v>
+        <v>-4.7491</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5733</v>
+        <v>-2.8111</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0604</v>
+        <v>-1.9381</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-4.6753</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>9.451500000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-14.1269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7997</v>
+        <v>-1.0475</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8159000000000003</v>
+        <v>-1.4243</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9835000000000002</v>
+        <v>0.3769</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1149</v>
+        <v>-0.505</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.918</v>
+        <v>-0.8629</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8031000000000001</v>
+        <v>0.3579</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9739</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7110000000000001</v>
+        <v>-0.6974</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2629</v>
+        <v>0.0789</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0889</v>
+        <v>0.1134</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6289</v>
+        <v>-0.1656</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4598999999999999</v>
+        <v>0.2789</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8747</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.464</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>5.3388</v>
+        <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3112</v>
+        <v>0.2789</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5659</v>
+        <v>0.2208</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.745</v>
+        <v>0.0581</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2483</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.8986</v>
+        <v>-1.2984</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.785500000000001</v>
+        <v>-0.7887000000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.113</v>
+        <v>-0.5094000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.4421</v>
+        <v>-1.1149</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2685999999999999</v>
+        <v>-1.918</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.7105</v>
+        <v>0.8031000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.8702</v>
+        <v>1.9739</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.133</v>
+        <v>0.7110000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.7374</v>
+        <v>1.2629</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5718</v>
+        <v>-3.0889</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4012999999999999</v>
+        <v>-2.6289</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9732000000000001</v>
+        <v>-0.4598999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8479</v>
+        <v>2.8747</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.464</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8479</v>
+        <v>5.3388</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7767</v>
+        <v>-0.8098</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.868</v>
+        <v>-0.5388000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9086000000000001</v>
+        <v>-0.2707</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5278</v>
+        <v>-2.2483</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.0472</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4805</v>
+        <v>-2.4885</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-7.903499999999999</v>
+        <v>-4.9933</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.4227</v>
+        <v>-4.9991</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4808</v>
+        <v>0.005699999999999941</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.8691</v>
+        <v>-4.4421</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.8014</v>
+        <v>0.2685999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0675</v>
+        <v>-4.7105</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.1754</v>
+        <v>-3.8702</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.122799999999999</v>
+        <v>-0.133</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9472</v>
+        <v>-3.7374</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.6933</v>
+        <v>-0.5718</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6787</v>
+        <v>0.4012999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0147</v>
+        <v>-0.9732000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.8749</v>
+        <v>1.8479</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.419</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5441</v>
+        <v>1.8479</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4543</v>
+        <v>-0.8715999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2193</v>
+        <v>-0.08149999999999996</v>
       </c>
       <c r="U16" t="n">
-        <v>0.235</v>
+        <v>-0.79</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.614</v>
+        <v>-1.5278</v>
       </c>
       <c r="W16" t="n">
-        <v>3.952500000000001</v>
+        <v>-1.0472</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.5666</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.975100000000001</v>
+        <v>-7.9353</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8349</v>
+        <v>-4.4458</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.139899999999999</v>
+        <v>-3.4895</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9079</v>
+        <v>-5.8691</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5368</v>
+        <v>-4.8014</v>
       </c>
       <c r="I17" t="n">
-        <v>4.371</v>
+        <v>-1.0675</v>
       </c>
       <c r="J17" t="n">
-        <v>17.8003</v>
+        <v>-2.1754</v>
       </c>
       <c r="K17" t="n">
-        <v>12.246</v>
+        <v>-3.122799999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>5.5543</v>
+        <v>0.9472</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.8928</v>
+        <v>-3.6933</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.7094</v>
+        <v>-1.6787</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1834</v>
+        <v>-2.0147</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0802</v>
+        <v>-2.8749</v>
       </c>
       <c r="Q17" t="n">
-        <v>-19.3019</v>
+        <v>-8.419</v>
       </c>
       <c r="R17" t="n">
-        <v>22.3825</v>
+        <v>5.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.2876</v>
+        <v>2.4225</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.784800000000001</v>
+        <v>2.1962</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.5026</v>
+        <v>0.2263</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.6753</v>
+        <v>-1.614</v>
       </c>
       <c r="W17" t="n">
-        <v>9.451500000000001</v>
+        <v>3.952500000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.1269</v>
+        <v>-5.5666</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-12.0537</v>
+        <v>-11.1104</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.1668</v>
+        <v>-9.650500000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.886899999999999</v>
+        <v>-1.4599</v>
       </c>
       <c r="G18" t="n">
         <v>-16.1581</v>
@@ -1858,13 +1858,13 @@
         <v>42.5058</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8352000000000004</v>
+        <v>1.7781</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3898</v>
+        <v>1.9062</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.5547</v>
+        <v>-0.1278000000000002</v>
       </c>
       <c r="V18" t="n">
         <v>-2.6853</v>
@@ -1891,19 +1891,19 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>248.5209</v>
+        <v>274.1505</v>
       </c>
       <c r="E19" t="n">
-        <v>195.1399</v>
+        <v>204.0332</v>
       </c>
       <c r="F19" t="n">
-        <v>53.38159999999999</v>
+        <v>70.11789999999999</v>
       </c>
       <c r="G19" t="n">
         <v>189.4756</v>
       </c>
       <c r="H19" t="n">
-        <v>68.75230000000001</v>
+        <v>68.75229999999999</v>
       </c>
       <c r="I19" t="n">
         <v>120.7245</v>
@@ -1927,7 +1927,7 @@
         <v>-61.2519</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0537</v>
+        <v>2.053699999999998</v>
       </c>
       <c r="Q19" t="n">
         <v>-386.0424</v>
@@ -1936,13 +1936,13 @@
         <v>388.0969</v>
       </c>
       <c r="S19" t="n">
-        <v>36.4976</v>
+        <v>62.1275</v>
       </c>
       <c r="T19" t="n">
-        <v>31.268</v>
+        <v>40.1607</v>
       </c>
       <c r="U19" t="n">
-        <v>5.230499999999999</v>
+        <v>21.9672</v>
       </c>
       <c r="V19" t="n">
         <v>20.4945</v>
